--- a/调研.xlsx
+++ b/调研.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17376\Desktop\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6977B65B-B03D-4B0E-82A0-2C63B272EE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B7FBE9-34B2-48B2-A542-517CA9ACD5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" xr2:uid="{FB23340B-0AE2-44D0-AA87-54856A235139}"/>
+    <workbookView xWindow="9435" yWindow="2355" windowWidth="28800" windowHeight="15345" xr2:uid="{FB23340B-0AE2-44D0-AA87-54856A235139}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="82">
   <si>
     <t>工具</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -333,6 +333,19 @@
   </si>
   <si>
     <t>DDL、dialect、user_input、TASK、RULES、Response Guidelines</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PostgreSQL、MySQL、通用 SQL、Snowflake、DataBricks、Google BigQuery、Yahoo Finance、Airtable
+此外，PandasAI 还提供了一个通用 SQL 连接器，可用于连接到任何 SQL 数据库。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DDL、TASK、QUERY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TASK、DDL、INPUT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -851,7 +864,9 @@
       <c r="D6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>81</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>48</v>
       </c>
@@ -890,18 +905,22 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="6"/>
+      <c r="C9" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="D9" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
